--- a/astro-site/public/dl/kit-plan-financiero/03-cash-flow-forecast.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/03-cash-flow-forecast.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Flujo Mensual" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Alertas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo Mensual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alertas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Flujo Mensual'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Alertas'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -141,47 +144,47 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="10" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -541,15 +544,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="85"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -557,6 +561,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -564,6 +569,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -592,9 +598,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -623,8 +627,25 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -633,24 +654,24 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="30"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="14"/>
-    <col customWidth="1" max="11" min="11" width="14"/>
-    <col customWidth="1" max="12" min="12" width="14"/>
-    <col customWidth="1" max="13" min="13" width="14"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -667,6 +688,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -745,47 +767,47 @@
       </c>
       <c r="C5" s="9">
         <f>B22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D5" s="9">
         <f>C22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E5" s="9">
         <f>D22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F5" s="9">
         <f>E22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G5" s="9">
         <f>F22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H5" s="9">
         <f>G22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I5" s="9">
         <f>H22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J5" s="9">
         <f>I22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K5" s="9">
         <f>J22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L5" s="9">
         <f>K22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M5" s="9">
         <f>L22</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -1018,51 +1040,51 @@
       </c>
       <c r="B12" s="9">
         <f>SUM(B7:B11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C12" s="9">
         <f>SUM(C7:C11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D12" s="9">
         <f>SUM(D7:D11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E12" s="9">
         <f>SUM(E7:E11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F12" s="9">
         <f>SUM(F7:F11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G12" s="9">
         <f>SUM(G7:G11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H12" s="9">
         <f>SUM(H7:H11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I12" s="9">
         <f>SUM(I7:I11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J12" s="9">
         <f>SUM(J7:J11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K12" s="9">
         <f>SUM(K7:K11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L12" s="9">
         <f>SUM(L7:L11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M12" s="9">
         <f>SUM(M7:M11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -1467,51 +1489,51 @@
       </c>
       <c r="B23" s="9">
         <f>SUM(B14:B22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C23" s="9">
         <f>SUM(C14:C22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D23" s="9">
         <f>SUM(D14:D22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E23" s="9">
         <f>SUM(E14:E22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F23" s="9">
         <f>SUM(F14:F22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G23" s="9">
         <f>SUM(G14:G22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H23" s="9">
         <f>SUM(H14:H22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I23" s="9">
         <f>SUM(I14:I22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J23" s="9">
         <f>SUM(J14:J22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K23" s="9">
         <f>SUM(K14:K22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L23" s="9">
         <f>SUM(L14:L22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M23" s="9">
         <f>SUM(M14:M22)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -1522,51 +1544,51 @@
       </c>
       <c r="B24" s="12">
         <f>B12-B23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C24" s="12">
         <f>C12-C23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D24" s="12">
         <f>D12-D23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E24" s="12">
         <f>E12-E23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F24" s="12">
         <f>F12-F23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G24" s="12">
         <f>G12-G23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H24" s="12">
         <f>H12-H23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I24" s="12">
         <f>I12-I23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J24" s="12">
         <f>J12-J23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K24" s="12">
         <f>K12-K23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L24" s="12">
         <f>L12-L23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M24" s="12">
         <f>M12-M23</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -1577,53 +1599,54 @@
       </c>
       <c r="B25" s="14">
         <f>B5+B24</f>
-        <v/>
+        <v>15000.0</v>
       </c>
       <c r="C25" s="14">
         <f>C5+C24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D25" s="14">
         <f>D5+D24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="14">
         <f>E5+E24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F25" s="14">
         <f>F5+F24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G25" s="14">
         <f>G5+G24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H25" s="14">
         <f>H5+H24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I25" s="14">
         <f>I5+I24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J25" s="14">
         <f>J5+J24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K25" s="14">
         <f>K5+K24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L25" s="14">
         <f>L5+L24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M25" s="14">
         <f>M5+M24</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
@@ -1637,7 +1660,16 @@
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1646,16 +1678,16 @@
   <sheetPr>
     <tabColor rgb="00D32F2F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="20"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="18"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1665,6 +1697,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="16" t="inlineStr">
         <is>
@@ -1675,6 +1708,7 @@
         <v>5000</v>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr"/>
       <c r="B5" s="6" t="inlineStr">
@@ -1701,11 +1735,11 @@
       </c>
       <c r="C6" s="17">
         <f>'Flujo Mensual'!B25</f>
-        <v/>
-      </c>
-      <c r="D6" s="18">
+        <v>15000.0</v>
+      </c>
+      <c r="D6" s="18" t="str">
         <f>IF(C6&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>OK</v>
       </c>
     </row>
     <row r="7">
@@ -1716,11 +1750,11 @@
       </c>
       <c r="C7" s="17">
         <f>'Flujo Mensual'!C25</f>
-        <v/>
-      </c>
-      <c r="D7" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="18" t="str">
         <f>IF(C7&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>⚠️ BAJO MÍNIMO</v>
       </c>
     </row>
     <row r="8">
@@ -1731,11 +1765,11 @@
       </c>
       <c r="C8" s="17">
         <f>'Flujo Mensual'!D25</f>
-        <v/>
-      </c>
-      <c r="D8" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="18" t="str">
         <f>IF(C8&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>⚠️ BAJO MÍNIMO</v>
       </c>
     </row>
     <row r="9">
@@ -1746,11 +1780,11 @@
       </c>
       <c r="C9" s="17">
         <f>'Flujo Mensual'!E25</f>
-        <v/>
-      </c>
-      <c r="D9" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="18" t="str">
         <f>IF(C9&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>⚠️ BAJO MÍNIMO</v>
       </c>
     </row>
     <row r="10">
@@ -1761,11 +1795,11 @@
       </c>
       <c r="C10" s="17">
         <f>'Flujo Mensual'!F25</f>
-        <v/>
-      </c>
-      <c r="D10" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D10" s="18" t="str">
         <f>IF(C10&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>⚠️ BAJO MÍNIMO</v>
       </c>
     </row>
     <row r="11">
@@ -1776,11 +1810,11 @@
       </c>
       <c r="C11" s="17">
         <f>'Flujo Mensual'!G25</f>
-        <v/>
-      </c>
-      <c r="D11" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="18" t="str">
         <f>IF(C11&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>⚠️ BAJO MÍNIMO</v>
       </c>
     </row>
     <row r="12">
@@ -1791,11 +1825,11 @@
       </c>
       <c r="C12" s="17">
         <f>'Flujo Mensual'!H25</f>
-        <v/>
-      </c>
-      <c r="D12" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D12" s="18" t="str">
         <f>IF(C12&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>⚠️ BAJO MÍNIMO</v>
       </c>
     </row>
     <row r="13">
@@ -1806,11 +1840,11 @@
       </c>
       <c r="C13" s="17">
         <f>'Flujo Mensual'!I25</f>
-        <v/>
-      </c>
-      <c r="D13" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D13" s="18" t="str">
         <f>IF(C13&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>⚠️ BAJO MÍNIMO</v>
       </c>
     </row>
     <row r="14">
@@ -1821,11 +1855,11 @@
       </c>
       <c r="C14" s="17">
         <f>'Flujo Mensual'!J25</f>
-        <v/>
-      </c>
-      <c r="D14" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D14" s="18" t="str">
         <f>IF(C14&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>⚠️ BAJO MÍNIMO</v>
       </c>
     </row>
     <row r="15">
@@ -1836,11 +1870,11 @@
       </c>
       <c r="C15" s="17">
         <f>'Flujo Mensual'!K25</f>
-        <v/>
-      </c>
-      <c r="D15" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D15" s="18" t="str">
         <f>IF(C15&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>⚠️ BAJO MÍNIMO</v>
       </c>
     </row>
     <row r="16">
@@ -1851,11 +1885,11 @@
       </c>
       <c r="C16" s="17">
         <f>'Flujo Mensual'!L25</f>
-        <v/>
-      </c>
-      <c r="D16" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="18" t="str">
         <f>IF(C16&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
+        <v>⚠️ BAJO MÍNIMO</v>
       </c>
     </row>
     <row r="17">
@@ -1866,13 +1900,15 @@
       </c>
       <c r="C17" s="17">
         <f>'Flujo Mensual'!M25</f>
-        <v/>
-      </c>
-      <c r="D17" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="D17" s="18" t="str">
         <f>IF(C17&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v/>
-      </c>
-    </row>
+        <v>⚠️ BAJO MÍNIMO</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
@@ -1885,6 +1921,15 @@
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-plan-financiero/03-cash-flow-forecast.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/03-cash-flow-forecast.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo Mensual" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alertas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parámetros" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo Mensual" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alertas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Flujo Mensual'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Alertas'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Flujo Mensual'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Alertas'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,8 +101,34 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +145,21 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -146,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,10 +223,79 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -254,6 +366,184 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Saldo final vs umbral de seguridad</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Alertas'!C5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Alertas'!$B$6:$B$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Alertas'!$C$6:$C$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Alertas'!E5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Alertas'!$B$6:$B$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Alertas'!$E$6:$E$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>€</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>AI Chef Pro</author>
+  </authors>
+  <commentList>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>Enero es input: aquí pagas el IVA del 4T del año ANTERIOR (modelo 303, del 1 al 30 de enero). Los demás meses los calcula la hoja sola en abril, julio y octubre.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -546,11 +836,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -587,7 +877,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>▸ El IVA trimestral se calcula automáticamente (línea 'Liquidación IVA').</t>
+          <t>▸ El IVA trimestral se calcula solo con los tipos de 'Parámetros' y el calendario del modelo 303 (abril, julio y octubre); enero queda como input, porque liquida el 4T del año anterior.</t>
         </is>
       </c>
     </row>
@@ -629,13 +919,55 @@
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+      <c r="B16" s="4" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>▸ En 'Parámetros' pones el % de cobro con tarjeta y su desfase, el plazo de pago a proveedores y la estacionalidad: la tesorería deja de ser una lista de deseos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>▸ El bloque gris del final («datos base») no es caja: son las compras y la Seguridad Social devengada del mes, de donde salen el pago a proveedores, la SS del mes siguiente y el IVA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Todas las cifras de esta plantilla van CON IVA: es caja. En el resto del kit (01, 01b, 02, 05, 06 y 07) van SIN IVA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Para editar una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -652,14 +984,408 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Parámetros de Tesorería</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Kit Plan Financiero para Restaurantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>% de ventas cobradas con tarjeta</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>El efectivo entra el mismo día; la tarjeta, con desfase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Días de abono de la tarjeta (D+n)</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>Lo que tarda tu TPV en ingresarte. Típico D+1 o D+2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Plazo de pago a proveedores (días)</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>El que hayas negociado. 0 = pago al contado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IVA repercutido en ventas (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Restauración: 10 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IVA soportado en compras de alimentación (%)</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Alimentación: 10 % (4 % en algunos básicos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IVA soportado en el resto de gastos (%)</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Alquiler, suministros, marketing, gestoría: 21 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>ESTACIONALIDAD (índice por mes; 1,00 = mes tipo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>Ventas sugeridas del mes (IVA incl.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ene</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="29">
+        <f>$C$26*$C13</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="29">
+        <f>$C$26*$C14</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="29">
+        <f>$C$26*$C15</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Abr</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="29">
+        <f>$C$26*$C16</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="29">
+        <f>$C$26*$C17</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="29">
+        <f>$C$26*$C18</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="29">
+        <f>$C$26*$C19</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ago</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="29">
+        <f>$C$26*$C20</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="29">
+        <f>$C$26*$C21</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="29">
+        <f>$C$26*$C22</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="29">
+        <f>$C$26*$C23</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dic</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="29">
+        <f>$C$26*$C24</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>Ventas de un mes tipo (IVA incl.)</t>
+        </is>
+      </c>
+      <c r="C26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>Escríbelo una vez y la estacionalidad te sugiere los doce meses; luego cópialos a «Flujo Mensual».</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Calendario del modelo 303: se presenta del 1 al 20 de abril, julio y octubre, y del 1 al 30 de enero. Por eso la liquidación sólo calcula en esos meses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>© 2026 AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <dataValidations count="2">
+    <dataValidation sqref="C5 C6 C26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C4 C7 C8 C9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -688,7 +1414,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>VALORES DE EJEMPLO — sustitúyelos por los tuyos</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -762,52 +1494,52 @@
           <t>SALDO INICIAL</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="33" t="n">
         <v>15000</v>
       </c>
       <c r="C5" s="9">
-        <f>B22</f>
-        <v>0.0</v>
+        <f>B29</f>
+        <v>15000.0</v>
       </c>
       <c r="D5" s="9">
-        <f>C22</f>
-        <v>0.0</v>
+        <f>C29</f>
+        <v>15000.0</v>
       </c>
       <c r="E5" s="9">
-        <f>D22</f>
-        <v>0.0</v>
+        <f>D29</f>
+        <v>15000.0</v>
       </c>
       <c r="F5" s="9">
-        <f>E22</f>
-        <v>0.0</v>
+        <f>E29</f>
+        <v>15000.0</v>
       </c>
       <c r="G5" s="9">
-        <f>F22</f>
-        <v>0.0</v>
+        <f>F29</f>
+        <v>15000.0</v>
       </c>
       <c r="H5" s="9">
-        <f>G22</f>
-        <v>0.0</v>
+        <f>G29</f>
+        <v>15000.0</v>
       </c>
       <c r="I5" s="9">
-        <f>H22</f>
-        <v>0.0</v>
+        <f>H29</f>
+        <v>15000.0</v>
       </c>
       <c r="J5" s="9">
-        <f>I22</f>
-        <v>0.0</v>
+        <f>I29</f>
+        <v>15000.0</v>
       </c>
       <c r="K5" s="9">
-        <f>J22</f>
-        <v>0.0</v>
+        <f>J29</f>
+        <v>15000.0</v>
       </c>
       <c r="L5" s="9">
-        <f>K22</f>
-        <v>0.0</v>
+        <f>K29</f>
+        <v>15000.0</v>
       </c>
       <c r="M5" s="9">
-        <f>L22</f>
-        <v>0.0</v>
+        <f>L29</f>
+        <v>15000.0</v>
       </c>
     </row>
     <row r="6">
@@ -823,40 +1555,40 @@
           <t>Ventas comedor (IVA incl.)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8" t="n">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -866,40 +1598,40 @@
           <t>Ventas barra (IVA incl.)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8" t="n">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -909,83 +1641,83 @@
           <t>Ventas delivery (IVA incl.)</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8" t="n">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Eventos / Catering</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="8" t="n">
+          <t>Eventos / Catering (IVA incl.)</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -995,47 +1727,47 @@
           <t>Otros cobros</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8" t="n">
+      <c r="B11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>TOTAL COBROS</t>
+          <t>VENTAS DEL MES</t>
         </is>
       </c>
       <c r="B12" s="9">
@@ -1088,578 +1820,1106 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Pendiente de abono de tarjeta (a cobrar el mes que viene)</t>
+        </is>
+      </c>
+      <c r="B13" s="29">
+        <f>IFERROR(B12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="29">
+        <f>IFERROR(C12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D13" s="29">
+        <f>IFERROR(D12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="29">
+        <f>IFERROR(E12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="29">
+        <f>IFERROR(F12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="29">
+        <f>IFERROR(G12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="29">
+        <f>IFERROR(H12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="29">
+        <f>IFERROR(I12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="29">
+        <f>IFERROR(J12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="29">
+        <f>IFERROR(K12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="L13" s="29">
+        <f>IFERROR(L12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M13" s="29">
+        <f>IFERROR(M12*Parámetros!$C$4*Parámetros!$C$5/30,0)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL COBROS DE CAJA</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>B12-B13</f>
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="9">
+        <f>C12-C13+B13</f>
+        <v>0.0</v>
+      </c>
+      <c r="D14" s="9">
+        <f>D12-D13+C13</f>
+        <v>0.0</v>
+      </c>
+      <c r="E14" s="9">
+        <f>E12-E13+D13</f>
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="9">
+        <f>F12-F13+E13</f>
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="9">
+        <f>G12-G13+F13</f>
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="9">
+        <f>H12-H13+G13</f>
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="9">
+        <f>I12-I13+H13</f>
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="9">
+        <f>J12-J13+I13</f>
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="9">
+        <f>K12-K13+J13</f>
+        <v>0.0</v>
+      </c>
+      <c r="L14" s="9">
+        <f>L12-L13+K13</f>
+        <v>0.0</v>
+      </c>
+      <c r="M14" s="9">
+        <f>M12-M13+L13</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>PAGOS (Salidas)</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Compras materia prima</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Nóminas + SS</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="34" t="n"/>
+      <c r="H15" s="34" t="n"/>
+      <c r="I15" s="34" t="n"/>
+      <c r="J15" s="34" t="n"/>
+      <c r="K15" s="34" t="n"/>
+      <c r="L15" s="34" t="n"/>
+      <c r="M15" s="34" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Alquiler</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>0</v>
+          <t>Pago a proveedores (según el plazo negociado)</t>
+        </is>
+      </c>
+      <c r="B16" s="17">
+        <f>IFERROR(B33*(1-Parámetros!$C$6/30),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C16" s="17">
+        <f>IFERROR(C33*(1-Parámetros!$C$6/30)+B33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="17">
+        <f>IFERROR(D33*(1-Parámetros!$C$6/30)+C33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E16" s="17">
+        <f>IFERROR(E33*(1-Parámetros!$C$6/30)+D33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="17">
+        <f>IFERROR(F33*(1-Parámetros!$C$6/30)+E33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="17">
+        <f>IFERROR(G33*(1-Parámetros!$C$6/30)+F33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="17">
+        <f>IFERROR(H33*(1-Parámetros!$C$6/30)+G33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="17">
+        <f>IFERROR(I33*(1-Parámetros!$C$6/30)+H33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="17">
+        <f>IFERROR(J33*(1-Parámetros!$C$6/30)+I33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="17">
+        <f>IFERROR(K33*(1-Parámetros!$C$6/30)+J33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="17">
+        <f>IFERROR(L33*(1-Parámetros!$C$6/30)+K33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M16" s="17">
+        <f>IFERROR(M33*(1-Parámetros!$C$6/30)+L33*Parámetros!$C$6/30,0)</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Suministros</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8" t="n">
+          <t>Nóminas (neto)</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>0</v>
+          <t>Pago de Seguridad Social (la del mes anterior)</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="17">
+        <f>B34</f>
+        <v>0.0</v>
+      </c>
+      <c r="D18" s="17">
+        <f>C34</f>
+        <v>0.0</v>
+      </c>
+      <c r="E18" s="17">
+        <f>D34</f>
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="17">
+        <f>E34</f>
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="17">
+        <f>F34</f>
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="17">
+        <f>G34</f>
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="17">
+        <f>H34</f>
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="17">
+        <f>I34</f>
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="17">
+        <f>J34</f>
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="17">
+        <f>K34</f>
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="17">
+        <f>L34</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Gestoría / Admin</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="8" t="n">
+          <t>Alquiler</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Cuota préstamo</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="8" t="n">
+          <t>Suministros</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Liquidación IVA trimestral</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8" t="n">
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Otros pagos</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="8" t="n">
+          <t>Gestoría / Admin</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Cuota de préstamo</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Retenciones IRPF (mod. 111)</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Liquidación de IVA (mod. 303) · enero = input (4T anterior)</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="D25" s="14">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E25" s="14">
+        <f>MAX(0,SUM($B$36:$D$36)-SUM($B$37:$D$37))</f>
+        <v>0.0</v>
+      </c>
+      <c r="F25" s="14">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="G25" s="14">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="H25" s="14">
+        <f>MAX(0,SUM($E$36:$G$36)-SUM($E$37:$G$37))</f>
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="14">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="J25" s="14">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="K25" s="14">
+        <f>MAX(0,SUM($H$36:$J$36)-SUM($H$37:$J$37))</f>
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="14">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="M25" s="14">
+        <f>""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Comisiones de plataformas de delivery y otros pagos</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>TOTAL PAGOS</t>
         </is>
       </c>
-      <c r="B23" s="9">
-        <f>SUM(B14:B22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="C23" s="9">
-        <f>SUM(C14:C22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="D23" s="9">
-        <f>SUM(D14:D22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E23" s="9">
-        <f>SUM(E14:E22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="F23" s="9">
-        <f>SUM(F14:F22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="9">
-        <f>SUM(G14:G22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H23" s="9">
-        <f>SUM(H14:H22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="9">
-        <f>SUM(I14:I22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="J23" s="9">
-        <f>SUM(J14:J22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="9">
-        <f>SUM(K14:K22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="9">
-        <f>SUM(L14:L22)</f>
-        <v>0.0</v>
-      </c>
-      <c r="M23" s="9">
-        <f>SUM(M14:M22)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>FLUJO NETO MES</t>
-        </is>
-      </c>
-      <c r="B24" s="12">
-        <f>B12-B23</f>
-        <v>0.0</v>
-      </c>
-      <c r="C24" s="12">
-        <f>C12-C23</f>
-        <v>0.0</v>
-      </c>
-      <c r="D24" s="12">
-        <f>D12-D23</f>
-        <v>0.0</v>
-      </c>
-      <c r="E24" s="12">
-        <f>E12-E23</f>
-        <v>0.0</v>
-      </c>
-      <c r="F24" s="12">
-        <f>F12-F23</f>
-        <v>0.0</v>
-      </c>
-      <c r="G24" s="12">
-        <f>G12-G23</f>
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="12">
-        <f>H12-H23</f>
-        <v>0.0</v>
-      </c>
-      <c r="I24" s="12">
-        <f>I12-I23</f>
-        <v>0.0</v>
-      </c>
-      <c r="J24" s="12">
-        <f>J12-J23</f>
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="12">
-        <f>K12-K23</f>
-        <v>0.0</v>
-      </c>
-      <c r="L24" s="12">
-        <f>L12-L23</f>
-        <v>0.0</v>
-      </c>
-      <c r="M24" s="12">
-        <f>M12-M23</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B27" s="9">
+        <f>SUM(B16:B26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C27" s="9">
+        <f>SUM(C16:C26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D27" s="9">
+        <f>SUM(D16:D26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E27" s="9">
+        <f>SUM(E16:E26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F27" s="9">
+        <f>SUM(F16:F26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G27" s="9">
+        <f>SUM(G16:G26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H27" s="9">
+        <f>SUM(H16:H26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="9">
+        <f>SUM(I16:I26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="J27" s="9">
+        <f>SUM(J16:J26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="9">
+        <f>SUM(K16:K26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="9">
+        <f>SUM(L16:L26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M27" s="9">
+        <f>SUM(M16:M26)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>FLUJO NETO DEL MES</t>
+        </is>
+      </c>
+      <c r="B28" s="9">
+        <f>B14-B27</f>
+        <v>0.0</v>
+      </c>
+      <c r="C28" s="9">
+        <f>C14-C27</f>
+        <v>0.0</v>
+      </c>
+      <c r="D28" s="9">
+        <f>D14-D27</f>
+        <v>0.0</v>
+      </c>
+      <c r="E28" s="9">
+        <f>E14-E27</f>
+        <v>0.0</v>
+      </c>
+      <c r="F28" s="9">
+        <f>F14-F27</f>
+        <v>0.0</v>
+      </c>
+      <c r="G28" s="9">
+        <f>G14-G27</f>
+        <v>0.0</v>
+      </c>
+      <c r="H28" s="9">
+        <f>H14-H27</f>
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="9">
+        <f>I14-I27</f>
+        <v>0.0</v>
+      </c>
+      <c r="J28" s="9">
+        <f>J14-J27</f>
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="9">
+        <f>K14-K27</f>
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="9">
+        <f>L14-L27</f>
+        <v>0.0</v>
+      </c>
+      <c r="M28" s="9">
+        <f>M14-M27</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>SALDO FINAL</t>
         </is>
       </c>
-      <c r="B25" s="14">
-        <f>B5+B24</f>
-        <v>15000.0</v>
-      </c>
-      <c r="C25" s="14">
-        <f>C5+C24</f>
-        <v>0.0</v>
-      </c>
-      <c r="D25" s="14">
-        <f>D5+D24</f>
-        <v>0.0</v>
-      </c>
-      <c r="E25" s="14">
-        <f>E5+E24</f>
-        <v>0.0</v>
-      </c>
-      <c r="F25" s="14">
-        <f>F5+F24</f>
-        <v>0.0</v>
-      </c>
-      <c r="G25" s="14">
-        <f>G5+G24</f>
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="14">
-        <f>H5+H24</f>
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="14">
-        <f>I5+I24</f>
-        <v>0.0</v>
-      </c>
-      <c r="J25" s="14">
-        <f>J5+J24</f>
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="14">
-        <f>K5+K24</f>
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="14">
-        <f>L5+L24</f>
-        <v>0.0</v>
-      </c>
-      <c r="M25" s="14">
-        <f>M5+M24</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="B29" s="9">
+        <f>B5+B28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="C29" s="9">
+        <f>C5+C28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="D29" s="9">
+        <f>D5+D28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="E29" s="9">
+        <f>E5+E28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="F29" s="9">
+        <f>F5+F28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="G29" s="9">
+        <f>G5+G28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="H29" s="9">
+        <f>H5+H28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="I29" s="9">
+        <f>I5+I28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="J29" s="9">
+        <f>J5+J28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="K29" s="9">
+        <f>K5+K28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="L29" s="9">
+        <f>L5+L28</f>
+        <v>15000.0</v>
+      </c>
+      <c r="M29" s="9">
+        <f>M5+M28</f>
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>DATOS BASE — no son caja, pero alimentan las filas de arriba</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="n"/>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="36" t="n"/>
+      <c r="I31" s="36" t="n"/>
+      <c r="J31" s="36" t="n"/>
+      <c r="K31" s="36" t="n"/>
+      <c r="L31" s="36" t="n"/>
+      <c r="M31" s="36" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="37" t="inlineStr">
+        <is>
+          <t>Compras de materia prima del mes (IVA incl.)</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>Seguridad Social devengada del mes</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>IVA repercutido del mes</t>
+        </is>
+      </c>
+      <c r="B36" s="38">
+        <f>IFERROR(B12-B12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C36" s="38">
+        <f>IFERROR(C12-C12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D36" s="38">
+        <f>IFERROR(D12-D12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E36" s="38">
+        <f>IFERROR(E12-E12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F36" s="38">
+        <f>IFERROR(F12-F12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G36" s="38">
+        <f>IFERROR(G12-G12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="38">
+        <f>IFERROR(H12-H12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I36" s="38">
+        <f>IFERROR(I12-I12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="J36" s="38">
+        <f>IFERROR(J12-J12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="38">
+        <f>IFERROR(K12-K12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="38">
+        <f>IFERROR(L12-L12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M36" s="38">
+        <f>IFERROR(M12-M12/(1+Parámetros!$C$7),0)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="37" t="inlineStr">
+        <is>
+          <t>IVA soportado del mes</t>
+        </is>
+      </c>
+      <c r="B37" s="38">
+        <f>IFERROR(B33-B33/(1+Parámetros!$C$8)+(B19+B20+B21+B22)-(B19+B20+B21+B22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C37" s="38">
+        <f>IFERROR(C33-C33/(1+Parámetros!$C$8)+(C19+C20+C21+C22)-(C19+C20+C21+C22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D37" s="38">
+        <f>IFERROR(D33-D33/(1+Parámetros!$C$8)+(D19+D20+D21+D22)-(D19+D20+D21+D22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E37" s="38">
+        <f>IFERROR(E33-E33/(1+Parámetros!$C$8)+(E19+E20+E21+E22)-(E19+E20+E21+E22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F37" s="38">
+        <f>IFERROR(F33-F33/(1+Parámetros!$C$8)+(F19+F20+F21+F22)-(F19+F20+F21+F22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G37" s="38">
+        <f>IFERROR(G33-G33/(1+Parámetros!$C$8)+(G19+G20+G21+G22)-(G19+G20+G21+G22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="38">
+        <f>IFERROR(H33-H33/(1+Parámetros!$C$8)+(H19+H20+H21+H22)-(H19+H20+H21+H22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I37" s="38">
+        <f>IFERROR(I33-I33/(1+Parámetros!$C$8)+(I19+I20+I21+I22)-(I19+I20+I21+I22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="J37" s="38">
+        <f>IFERROR(J33-J33/(1+Parámetros!$C$8)+(J19+J20+J21+J22)-(J19+J20+J21+J22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="K37" s="38">
+        <f>IFERROR(K33-K33/(1+Parámetros!$C$8)+(K19+K20+K21+K22)-(K19+K20+K21+K22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="L37" s="38">
+        <f>IFERROR(L33-L33/(1+Parámetros!$C$8)+(L19+L20+L21+L22)-(L19+L20+L21+L22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="M37" s="38">
+        <f>IFERROR(M33-M33/(1+Parámetros!$C$8)+(M19+M20+M21+M22)-(M19+M20+M21+M22)/(1+Parámetros!$C$9),0)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="37" t="inlineStr">
+        <is>
+          <t>Ventas sugeridas por estacionalidad (informativo)</t>
+        </is>
+      </c>
+      <c r="B39" s="38">
+        <f>Parámetros!$D$13</f>
+        <v>0.0</v>
+      </c>
+      <c r="C39" s="38">
+        <f>Parámetros!$D$14</f>
+        <v>0.0</v>
+      </c>
+      <c r="D39" s="38">
+        <f>Parámetros!$D$15</f>
+        <v>0.0</v>
+      </c>
+      <c r="E39" s="38">
+        <f>Parámetros!$D$16</f>
+        <v>0.0</v>
+      </c>
+      <c r="F39" s="38">
+        <f>Parámetros!$D$17</f>
+        <v>0.0</v>
+      </c>
+      <c r="G39" s="38">
+        <f>Parámetros!$D$18</f>
+        <v>0.0</v>
+      </c>
+      <c r="H39" s="38">
+        <f>Parámetros!$D$19</f>
+        <v>0.0</v>
+      </c>
+      <c r="I39" s="38">
+        <f>Parámetros!$D$20</f>
+        <v>0.0</v>
+      </c>
+      <c r="J39" s="38">
+        <f>Parámetros!$D$21</f>
+        <v>0.0</v>
+      </c>
+      <c r="K39" s="38">
+        <f>Parámetros!$D$22</f>
+        <v>0.0</v>
+      </c>
+      <c r="L39" s="38">
+        <f>Parámetros!$D$23</f>
+        <v>0.0</v>
+      </c>
+      <c r="M39" s="38">
+        <f>Parámetros!$D$24</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A27:M27"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B7 B8 B9 B10 B11 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B33 B34 C7 C8 C9 C10 C11 C17 C19 C20 C21 C22 C23 C24 C26 C33 C34 D7 D8 D9 D10 D11 D17 D19 D20 D21 D22 D23 D24 D26 D33 D34 E7 E8 E9 E10 E11 E17 E19 E20 E21 E22 E23 E24 E26 E33 E34 F7 F8 F9 F10 F11 F17 F19 F20 F21 F22 F23 F24 F26 F33 F34 G7 G8 G9 G10 G11 G17 G19 G20 G21 G22 G23 G24 G26 G33 G34 H7 H8 H9 H10 H11 H17 H19 H20 H21 H22 H23 H24 H26 H33 H34 I7 I8 I9 I10 I11 I17 I19 I20 I21 I22 I23 I24 I26 I33 I34 J7 J8 J9 J10 J11 J17 J19 J20 J21 J22 J23 J24 J26 J33 J34 K7 K8 K9 K10 K11 K17 K19 K20 K21 K22 K23 K24 K26 K33 K34 L7 L8 L9 L10 L11 L17 L19 L20 L21 L22 L23 L24 L26 L33 L34 M7 M8 M9 M10 M11 M17 M19 M20 M21 M22 M23 M24 M26 M33 M34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número (puede ser negativo)." type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000000</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1670,10 +2930,11 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D32F2F"/>
@@ -1684,9 +2945,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1704,7 +2965,7 @@
           <t>Umbral de seguridad (€):</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="39" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -1726,6 +2987,11 @@
           <t>Alerta</t>
         </is>
       </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Umbral</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="11" t="inlineStr">
@@ -1734,12 +3000,16 @@
         </is>
       </c>
       <c r="C6" s="17">
-        <f>'Flujo Mensual'!B25</f>
+        <f>'Flujo Mensual'!B29</f>
         <v>15000.0</v>
       </c>
       <c r="D6" s="18" t="str">
-        <f>IF(C6&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>OK</v>
+        <f>IF('Flujo Mensual'!B12+'Flujo Mensual'!B27=0,"—",IF(C6&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E6" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="7">
@@ -1749,12 +3019,16 @@
         </is>
       </c>
       <c r="C7" s="17">
-        <f>'Flujo Mensual'!C25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!C29</f>
+        <v>15000.0</v>
       </c>
       <c r="D7" s="18" t="str">
-        <f>IF(C7&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!C12+'Flujo Mensual'!C27=0,"—",IF(C7&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E7" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="8">
@@ -1764,12 +3038,16 @@
         </is>
       </c>
       <c r="C8" s="17">
-        <f>'Flujo Mensual'!D25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!D29</f>
+        <v>15000.0</v>
       </c>
       <c r="D8" s="18" t="str">
-        <f>IF(C8&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!D12+'Flujo Mensual'!D27=0,"—",IF(C8&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E8" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="9">
@@ -1779,12 +3057,16 @@
         </is>
       </c>
       <c r="C9" s="17">
-        <f>'Flujo Mensual'!E25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!E29</f>
+        <v>15000.0</v>
       </c>
       <c r="D9" s="18" t="str">
-        <f>IF(C9&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!E12+'Flujo Mensual'!E27=0,"—",IF(C9&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E9" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="10">
@@ -1794,12 +3076,16 @@
         </is>
       </c>
       <c r="C10" s="17">
-        <f>'Flujo Mensual'!F25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!F29</f>
+        <v>15000.0</v>
       </c>
       <c r="D10" s="18" t="str">
-        <f>IF(C10&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!F12+'Flujo Mensual'!F27=0,"—",IF(C10&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E10" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="11">
@@ -1809,12 +3095,16 @@
         </is>
       </c>
       <c r="C11" s="17">
-        <f>'Flujo Mensual'!G25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!G29</f>
+        <v>15000.0</v>
       </c>
       <c r="D11" s="18" t="str">
-        <f>IF(C11&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!G12+'Flujo Mensual'!G27=0,"—",IF(C11&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E11" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="12">
@@ -1824,12 +3114,16 @@
         </is>
       </c>
       <c r="C12" s="17">
-        <f>'Flujo Mensual'!H25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!H29</f>
+        <v>15000.0</v>
       </c>
       <c r="D12" s="18" t="str">
-        <f>IF(C12&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!H12+'Flujo Mensual'!H27=0,"—",IF(C12&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E12" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="13">
@@ -1839,12 +3133,16 @@
         </is>
       </c>
       <c r="C13" s="17">
-        <f>'Flujo Mensual'!I25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!I29</f>
+        <v>15000.0</v>
       </c>
       <c r="D13" s="18" t="str">
-        <f>IF(C13&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!I12+'Flujo Mensual'!I27=0,"—",IF(C13&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E13" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="14">
@@ -1854,12 +3152,16 @@
         </is>
       </c>
       <c r="C14" s="17">
-        <f>'Flujo Mensual'!J25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!J29</f>
+        <v>15000.0</v>
       </c>
       <c r="D14" s="18" t="str">
-        <f>IF(C14&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!J12+'Flujo Mensual'!J27=0,"—",IF(C14&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E14" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="15">
@@ -1869,12 +3171,16 @@
         </is>
       </c>
       <c r="C15" s="17">
-        <f>'Flujo Mensual'!K25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!K29</f>
+        <v>15000.0</v>
       </c>
       <c r="D15" s="18" t="str">
-        <f>IF(C15&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!K12+'Flujo Mensual'!K27=0,"—",IF(C15&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E15" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="16">
@@ -1884,12 +3190,16 @@
         </is>
       </c>
       <c r="C16" s="17">
-        <f>'Flujo Mensual'!L25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!L29</f>
+        <v>15000.0</v>
       </c>
       <c r="D16" s="18" t="str">
-        <f>IF(C16&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!L12+'Flujo Mensual'!L27=0,"—",IF(C16&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E16" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="17">
@@ -1899,16 +3209,26 @@
         </is>
       </c>
       <c r="C17" s="17">
-        <f>'Flujo Mensual'!M25</f>
-        <v>0.0</v>
+        <f>'Flujo Mensual'!M29</f>
+        <v>15000.0</v>
       </c>
       <c r="D17" s="18" t="str">
-        <f>IF(C17&lt;$C$3,"⚠️ BAJO MÍNIMO","OK")</f>
-        <v>⚠️ BAJO MÍNIMO</v>
+        <f>IF('Flujo Mensual'!M12+'Flujo Mensual'!M27=0,"—",IF(C17&lt;$C$3,"⚠️ BAJO MÍNIMO","OK"))</f>
+        <v>—</v>
+      </c>
+      <c r="E17" s="29">
+        <f>$C$3</f>
+        <v>5000.0</v>
       </c>
     </row>
     <row r="18"/>
-    <row r="19"/>
+    <row r="19">
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>El estado «—» significa que ese mes todavía no tiene ni cobros ni pagos: el semáforo no opina sobre un mes vacío.</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
@@ -1917,10 +3237,29 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="B1:E1"/>
   </mergeCells>
+  <conditionalFormatting sqref="D6:D17">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" stopIfTrue="1" text="BAJO MÍNIMO">
+      <formula>NOT(ISERROR(SEARCH("BAJO MÍNIMO",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",D6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:C17">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="1">
+      <formula>=AND($C6&lt;$C$3,$D6&lt;&gt;"—")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1931,5 +3270,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>